--- a/back-end/mkd_works_service/api/templates/month_act/mkd_services_month_act_template.xlsx
+++ b/back-end/mkd_works_service/api/templates/month_act/mkd_services_month_act_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Projects\Housing Company Services(HCS)\back-end\mkd_works_service\api\templates\month_act\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{525A7E14-7099-4485-A513-E3FB709E1E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F981BF-26D2-49A3-91B5-50A062356667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -590,7 +590,7 @@
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.140625" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" customWidth="1"/>
     <col min="2" max="2" width="30.140625" customWidth="1"/>
     <col min="3" max="3" width="42.42578125" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
